--- a/data/ENVS2018 kioloa camera data 2025.xlsx
+++ b/data/ENVS2018 kioloa camera data 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f3a69dc1a79d235a/2 PhD/GIT/ENVS2018-environmental-science-field-school/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f3a69dc1a79d235a/1 Ecology work/GIT/ENVS2018/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="500" documentId="13_ncr:1_{4923BF50-181C-49E0-B701-65F6BFF95386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCDFEC5C-5E79-4701-B04B-42B5BD66567E}"/>
+  <xr:revisionPtr revIDLastSave="615" documentId="13_ncr:1_{4923BF50-181C-49E0-B701-65F6BFF95386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83A0567C-0337-4551-812E-578662665EB9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0855291B-83FE-4C3F-9AEC-A841D89559E4}"/>
+    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0855291B-83FE-4C3F-9AEC-A841D89559E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Camera data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="42">
   <si>
     <t>Group</t>
   </si>
@@ -84,27 +84,18 @@
     <t>B</t>
   </si>
   <si>
-    <t>Rattus lutreolus</t>
-  </si>
-  <si>
     <t xml:space="preserve">Swamp Wallaby </t>
   </si>
   <si>
     <t>Wallabia bicolor</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>G</t>
   </si>
   <si>
     <t>Note</t>
   </si>
   <si>
-    <t>Swamp Rat</t>
-  </si>
-  <si>
     <t>Trichosurus vulpecula</t>
   </si>
   <si>
@@ -114,52 +105,64 @@
     <t>H</t>
   </si>
   <si>
-    <t>Wonga Pigeon</t>
-  </si>
-  <si>
-    <t>Leucosarcia melanoleuca</t>
-  </si>
-  <si>
-    <t>Bos taurus</t>
-  </si>
-  <si>
-    <t>Mus musculus</t>
-  </si>
-  <si>
     <t>Nights deployed</t>
   </si>
   <si>
-    <t>Not formatted - camera fail</t>
-  </si>
-  <si>
-    <t>Literally just a wild Sho (no animals detected) but camera working</t>
-  </si>
-  <si>
-    <t>Black Rat</t>
-  </si>
-  <si>
-    <t>No animals recorded- just photos of grass blowing in wind.</t>
-  </si>
-  <si>
-    <t>Felis catus</t>
-  </si>
-  <si>
-    <t>Not deployed here this year due to time constraints</t>
-  </si>
-  <si>
-    <t>Cow</t>
-  </si>
-  <si>
-    <t>Rattus rattus</t>
-  </si>
-  <si>
     <t>Bush Rat</t>
   </si>
   <si>
-    <t>Cat</t>
-  </si>
-  <si>
-    <t>House Mouse</t>
+    <t>Vombatus ursinus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E </t>
+  </si>
+  <si>
+    <t>Camera failed low battery</t>
+  </si>
+  <si>
+    <t>No animals on camera but camera worked</t>
+  </si>
+  <si>
+    <t>No data recorded</t>
+  </si>
+  <si>
+    <t>Macropus giganteus</t>
+  </si>
+  <si>
+    <t>Malurus cyaneus</t>
+  </si>
+  <si>
+    <t>Lampropholis delicata</t>
+  </si>
+  <si>
+    <t>Torn left ear</t>
+  </si>
+  <si>
+    <t>Brown Antechinus</t>
+  </si>
+  <si>
+    <t>Superb Lyrebird</t>
+  </si>
+  <si>
+    <t>Common Wombat</t>
+  </si>
+  <si>
+    <t>Menura novaehollandiae</t>
+  </si>
+  <si>
+    <t>Superb Fairywren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern Grey Kangaroo </t>
+  </si>
+  <si>
+    <t>Delicate Sun-skink</t>
+  </si>
+  <si>
+    <t>Antechinus stuartii</t>
+  </si>
+  <si>
+    <t>No data reported (unclear if collected/analysed)</t>
   </si>
 </sst>
 </file>
@@ -169,7 +172,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,13 +211,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -236,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -248,7 +244,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -264,10 +259,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -567,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0587933C-DFD8-4B0D-926D-C9791FA23C2A}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.453125" style="1" bestFit="1" customWidth="1"/>
@@ -592,24 +583,24 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>24</v>
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2" s="10">
-        <v>45910</v>
+        <v>46281</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -617,265 +608,268 @@
         <v>14</v>
       </c>
       <c r="B3" s="10">
-        <v>45910</v>
+        <v>46280</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B4" s="10">
-        <v>45909</v>
+        <v>46280</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B5" s="10">
-        <v>45910</v>
+        <v>46280</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="10">
-        <v>45911</v>
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46281</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B7" s="10">
-        <v>45909</v>
+        <v>46280</v>
       </c>
       <c r="C7" s="9">
-        <v>15</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>22</v>
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>45909</v>
+        <v>46282</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1">
-        <v>45939</v>
+      <c r="A9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="10">
+        <v>46282</v>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B10" s="10">
-        <v>45910</v>
+        <v>46281</v>
       </c>
       <c r="C10">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>38</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" s="10">
-        <v>45909</v>
+        <v>46281</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="10">
-        <v>45909</v>
+        <v>46281</v>
       </c>
       <c r="C12">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>18</v>
+      <c r="A13" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="B13" s="10">
-        <v>45909</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
+        <v>46280</v>
+      </c>
+      <c r="C13" s="9">
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C14">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="10">
-        <v>45909</v>
-      </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1">
-        <v>45939</v>
+      <c r="B15" s="10">
+        <v>46281</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46281</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="10">
-        <v>45910</v>
-      </c>
-      <c r="C16">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
-        <v>24</v>
-      </c>
       <c r="B17" s="10">
-        <v>45911</v>
+        <v>46282</v>
       </c>
       <c r="C17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="10">
-        <v>45911</v>
+        <v>46282</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
@@ -888,56 +882,22 @@
       <c r="A19" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="10">
-        <v>45911</v>
+      <c r="B19" s="1">
+        <v>46281</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="10">
-        <v>45912</v>
-      </c>
-      <c r="C20">
-        <v>6</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="10">
-        <v>45911</v>
-      </c>
-      <c r="C21" s="9">
-        <v>15</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E22">
-    <sortCondition ref="D2:D22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F19">
+    <sortCondition ref="C1:C19"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -961,7 +921,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -970,122 +930,112 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="9">
-        <v>15</v>
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" s="9">
-        <v>3</v>
-      </c>
-      <c r="D2" s="9"/>
+        <v>2</v>
+      </c>
+      <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="9">
-        <v>8</v>
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>14</v>
       </c>
       <c r="C3" s="9">
-        <v>3</v>
-      </c>
-      <c r="D3" s="9"/>
+        <v>2</v>
+      </c>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="9">
-        <v>21</v>
-      </c>
-      <c r="C4" s="9">
-        <v>3</v>
-      </c>
-      <c r="D4" s="9"/>
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>22</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="6" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="9">
-        <v>7</v>
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
       </c>
       <c r="C5" s="9">
-        <v>3</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>30</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="9">
-        <v>20</v>
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>13</v>
       </c>
       <c r="C6" s="9">
-        <v>3</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>30</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="9">
-        <v>9</v>
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
       </c>
       <c r="C7" s="9">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>30</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="9">
+        <v>3</v>
       </c>
       <c r="C8" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>24</v>
+        <v>7</v>
+      </c>
+      <c r="B9" s="9">
+        <v>17</v>
       </c>
       <c r="C9" s="9">
-        <v>3</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>30</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="B10" s="9">
+        <v>18</v>
       </c>
       <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>30</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -1095,7 +1045,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="6"/>
     </row>
@@ -1104,75 +1054,75 @@
         <v>9</v>
       </c>
       <c r="B12">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C12" s="9">
-        <v>3</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>31</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C13" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C15" s="9">
         <v>2</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C16" s="9">
         <v>2</v>
       </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="6" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C17" s="9">
         <v>2</v>
@@ -1181,60 +1131,62 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C18" s="9">
         <v>2</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19">
+        <v>24</v>
+      </c>
+      <c r="C19" s="9">
+        <v>2</v>
+      </c>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="9">
         <v>7</v>
       </c>
-      <c r="B19">
-        <v>18</v>
-      </c>
-      <c r="C19" s="9">
-        <v>2</v>
-      </c>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
       <c r="C20" s="9">
         <v>2</v>
       </c>
       <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21">
-        <v>13</v>
+      <c r="A21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="9">
+        <v>9</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
       </c>
-      <c r="D21" s="6"/>
+      <c r="D21" s="6" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22">
-        <v>23</v>
+      <c r="A22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="9">
+        <v>20</v>
       </c>
       <c r="C22" s="9">
         <v>2</v>
@@ -1242,41 +1194,39 @@
       <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>13</v>
+      <c r="A23" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="B23">
-        <v>22</v>
-      </c>
-      <c r="C23" s="9">
-        <v>2</v>
-      </c>
-      <c r="D23" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="6" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>13</v>
+      <c r="A24" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C24" s="9">
         <v>2</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="9"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>13</v>
+      <c r="A25" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="B25">
-        <v>14</v>
-      </c>
-      <c r="C25" s="9">
-        <v>0</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C25" s="9"/>
       <c r="D25" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1326,6 +1276,9 @@
       <c r="C39" s="9"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D25">
+    <sortCondition ref="A1:A25"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>